--- a/lit_review_results/2-screening_phase/second_screening_summary.xlsx
+++ b/lit_review_results/2-screening_phase/second_screening_summary.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wolfrieder/PycharmProjects/sok_artifacts/lit_review_results/2-screening_phase/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D76B50-0A52-8249-BFA1-9D916CE4563F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B1A738-B51E-704D-A306-C25AD4BA774C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7740" yWindow="-28240" windowWidth="51080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17360" yWindow="-28240" windowWidth="51080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AK$302</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AW$303</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -7253,7 +7253,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:AY303"/>
+  <dimension ref="A1:AY304"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" style="1" bestFit="1" customWidth="1"/>
@@ -8463,7 +8463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:49" s="4" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:49" s="4" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>12</v>
       </c>
@@ -8717,7 +8717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:49" s="4" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:49" s="4" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
@@ -8844,7 +8844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:49" s="4" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:49" s="4" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>11</v>
       </c>
@@ -9747,7 +9747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:49" s="4" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:49" s="4" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>12</v>
       </c>
@@ -9876,7 +9876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:49" s="4" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:49" s="4" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>10</v>
       </c>
@@ -10134,7 +10134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:49" s="4" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:49" s="4" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>10</v>
       </c>
@@ -10263,7 +10263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:49" s="4" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:49" s="4" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>10</v>
       </c>
@@ -10650,7 +10650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:49" s="4" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:49" s="4" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>10</v>
       </c>
@@ -11166,7 +11166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:49" s="4" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:49" s="4" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>15</v>
       </c>
@@ -11424,7 +11424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:49" s="4" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:49" s="4" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>12</v>
       </c>
@@ -12843,7 +12843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:49" s="4" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:49" s="4" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>12</v>
       </c>
@@ -12972,7 +12972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:49" s="4" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:49" s="4" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>10</v>
       </c>
@@ -13617,7 +13617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:50" s="4" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:50" s="4" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>11</v>
       </c>
@@ -13749,7 +13749,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="51" spans="1:50" s="4" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:50" s="4" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>15</v>
       </c>
@@ -14390,7 +14390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:50" s="4" customFormat="1" ht="325" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:50" s="4" customFormat="1" ht="325" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>12</v>
       </c>
@@ -15036,7 +15036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:50" s="4" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:50" s="4" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>13</v>
       </c>
@@ -15424,7 +15424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:50" s="4" customFormat="1" ht="291" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:50" s="4" customFormat="1" ht="291" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>10</v>
       </c>
@@ -15553,7 +15553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:49" s="4" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:49" s="4" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>12</v>
       </c>
@@ -15940,7 +15940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:49" s="4" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:49" s="4" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>12</v>
       </c>
@@ -17426,7 +17426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:49" s="4" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:49" s="4" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>12</v>
       </c>
@@ -18196,7 +18196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:49" s="4" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:49" s="4" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>12</v>
       </c>
@@ -18325,7 +18325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:49" s="4" customFormat="1" ht="121" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:49" s="4" customFormat="1" ht="121" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>11</v>
       </c>
@@ -19099,7 +19099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:49" s="4" customFormat="1" ht="390" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:49" s="4" customFormat="1" ht="390" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>12</v>
       </c>
@@ -19228,7 +19228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:49" s="4" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:49" s="4" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>16</v>
       </c>
@@ -19350,7 +19350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:49" s="4" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:49" s="4" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>13</v>
       </c>
@@ -19608,7 +19608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:50" s="4" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:50" s="4" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>12</v>
       </c>
@@ -20256,7 +20256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:50" s="4" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:50" s="4" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>12</v>
       </c>
@@ -21414,7 +21414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:50" s="4" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:50" s="4" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>13</v>
       </c>
@@ -22315,7 +22315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:50" s="4" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:50" s="4" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>12</v>
       </c>
@@ -22573,7 +22573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:50" s="4" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:50" s="4" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>12</v>
       </c>
@@ -23211,7 +23211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:50" s="4" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:50" s="4" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
         <v>15</v>
       </c>
@@ -23596,7 +23596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:50" s="4" customFormat="1" ht="342" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:50" s="4" customFormat="1" ht="342" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
         <v>15</v>
       </c>
@@ -23728,7 +23728,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="129" spans="1:51" s="4" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:51" s="4" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
         <v>11</v>
       </c>
@@ -26166,7 +26166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:50" s="4" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:50" s="4" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>13</v>
       </c>
@@ -26807,7 +26807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:50" s="4" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:50" s="4" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>13</v>
       </c>
@@ -27579,7 +27579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:50" s="4" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:50" s="4" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
         <v>10</v>
       </c>
@@ -27711,7 +27711,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="160" spans="1:50" s="4" customFormat="1" ht="223" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:50" s="4" customFormat="1" ht="223" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
         <v>11</v>
       </c>
@@ -29259,7 +29259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:49" s="4" customFormat="1" ht="240" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:49" s="4" customFormat="1" ht="240" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
         <v>10</v>
       </c>
@@ -29902,7 +29902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:49" s="4" customFormat="1" ht="274" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:49" s="4" customFormat="1" ht="274" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
         <v>12</v>
       </c>
@@ -34603,7 +34603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:49" s="4" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:49" s="4" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
         <v>16</v>
       </c>
@@ -36912,7 +36912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:50" s="4" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:50" s="4" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
         <v>13</v>
       </c>
@@ -37551,7 +37551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:50" s="4" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:50" s="4" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
         <v>15</v>
       </c>
@@ -40647,7 +40647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:49" s="4" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:49" s="4" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
         <v>11</v>
       </c>
@@ -40776,7 +40776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:49" s="4" customFormat="1" ht="138" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:49" s="4" customFormat="1" ht="138" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
         <v>13</v>
       </c>
@@ -41808,7 +41808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:49" s="4" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:49" s="4" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
         <v>12</v>
       </c>
@@ -41937,7 +41937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:49" s="4" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:49" s="4" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
         <v>11</v>
       </c>
@@ -42324,7 +42324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:51" s="4" customFormat="1" ht="206" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:51" s="4" customFormat="1" ht="206" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
         <v>12</v>
       </c>
@@ -42580,7 +42580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:51" s="4" customFormat="1" ht="172" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:51" s="4" customFormat="1" ht="172" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
         <v>12</v>
       </c>
@@ -43096,7 +43096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:51" s="4" customFormat="1" ht="189" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:51" s="4" customFormat="1" ht="189" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
         <v>12</v>
       </c>
@@ -43610,7 +43610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:51" s="4" customFormat="1" ht="155" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:51" s="4" customFormat="1" ht="155" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
         <v>12</v>
       </c>
@@ -44902,7 +44902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:49" s="4" customFormat="1" ht="257" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:49" s="4" customFormat="1" ht="257" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A295" s="4" t="s">
         <v>12</v>
       </c>
@@ -45685,12 +45685,13 @@
       <c r="I302" s="23"/>
       <c r="J302" s="20"/>
     </row>
-    <row r="303" spans="1:49" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="303" spans="1:49" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="304" spans="1:49" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="A1:AK302" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="36">
+  <autoFilter ref="A1:AW303" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="42">
       <filters>
-        <filter val="Different"/>
+        <filter val="TRUE"/>
       </filters>
     </filterColumn>
   </autoFilter>
